--- a/artfynd/A 13230-2023 artfynd.xlsx
+++ b/artfynd/A 13230-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 13230-2023 artfynd.xlsx
+++ b/artfynd/A 13230-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>88893431</v>
+        <v>88893314</v>
       </c>
       <c r="B2" t="n">
-        <v>92688</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,41 +686,40 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2387</v>
+        <v>1205</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hagtorp 300 m sso, Srm</t>
+          <t>Hagtorp 200 m sso, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592950.084314719</v>
+        <v>592976</v>
       </c>
       <c r="R2" t="n">
-        <v>6546765.044326385</v>
+        <v>6546897</v>
       </c>
       <c r="S2" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,19 +746,9 @@
           <t>2020-10-27</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-10-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,18 +757,12 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>blandskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -802,15 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>88893331</v>
+        <v>88893431</v>
       </c>
       <c r="B3" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95962</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -818,21 +791,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>2387</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -842,17 +815,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hagtorp 200 m sso, Srm</t>
+          <t>Hagtorp 300 m sso, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592975.7558024239</v>
+        <v>592950</v>
       </c>
       <c r="R3" t="n">
-        <v>6546896.898417538</v>
+        <v>6546765</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,19 +852,9 @@
           <t>2020-10-27</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-10-27</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,12 +863,18 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>blandskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -923,15 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>88893314</v>
+        <v>88893331</v>
       </c>
       <c r="B4" t="n">
-        <v>89403</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -939,26 +903,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1205</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -966,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>592975.7558024239</v>
+        <v>592976</v>
       </c>
       <c r="R4" t="n">
-        <v>6546896.898417538</v>
+        <v>6546897</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -999,19 +964,9 @@
           <t>2020-10-27</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-10-27</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 13230-2023 artfynd.xlsx
+++ b/artfynd/A 13230-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -892,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>88893331</v>
+        <v>134723069</v>
       </c>
       <c r="B4" t="n">
-        <v>101326</v>
+        <v>75354</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,41 +903,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>6427</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Glansfläck</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Diarthonis spadicea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Leight.) Frisch &amp; al.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hagtorp 200 m sso, Srm</t>
+          <t>Lövgården, Lövgården, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>592976</v>
+        <v>592961</v>
       </c>
       <c r="R4" t="n">
-        <v>6546897</v>
+        <v>6546780</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -961,12 +957,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-10-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-10-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -977,24 +973,125 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Marcus Arnesson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Marcus Arnesson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>88893331</v>
+      </c>
+      <c r="B5" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hagtorp 200 m sso, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>592976</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6546897</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2020-10-27</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2020-10-27</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Bo Karlsson</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Bo Karlsson, Björn Rösch, Rolf Olsson, Bo Törnquist</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 13230-2023 artfynd.xlsx
+++ b/artfynd/A 13230-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88893314</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -889,6 +899,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88893431</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -986,6 +1001,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134723069</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1092,8 +1112,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88893331</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 13230-2023 artfynd.xlsx
+++ b/artfynd/A 13230-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1009,10 +1009,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>88893331</v>
+        <v>136299673</v>
       </c>
       <c r="B5" t="n">
-        <v>101326</v>
+        <v>4777</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1020,41 +1020,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>100299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hagtorp 200 m sso, Srm</t>
+          <t>Johannislund, Johannislund, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592976</v>
+        <v>592873</v>
       </c>
       <c r="R5" t="n">
-        <v>6546897</v>
+        <v>6546699</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1078,12 +1074,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2020-10-27</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2020-10-27</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1094,27 +1090,337 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Marcus Arnesson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bo Karlsson, Björn Rösch, Rolf Olsson, Bo Törnquist</t>
+          <t>Marcus Arnesson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136299673</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136299623</v>
+      </c>
+      <c r="B6" t="n">
+        <v>5202</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Johannislund, Johannislund, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>592927</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6546729</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Marcus Arnesson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Marcus Arnesson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136299623</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>88893331</v>
+      </c>
+      <c r="B7" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hagtorp 200 m sso, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>592976</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6546897</v>
+      </c>
+      <c r="S7" t="n">
+        <v>50</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2020-10-27</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2020-10-27</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Bo Karlsson, Björn Rösch, Rolf Olsson, Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/88893331</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136298255</v>
+      </c>
+      <c r="B8" t="n">
+        <v>101512</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lövgården, Lövgården, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>593062</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6546946</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Marcus Arnesson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Marcus Arnesson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136298255</t>
         </is>
       </c>
     </row>
@@ -1124,6 +1430,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 13230-2023 artfynd.xlsx
+++ b/artfynd/A 13230-2023 artfynd.xlsx
@@ -1327,7 +1327,7 @@
         <v>136298255</v>
       </c>
       <c r="B8" t="n">
-        <v>101512</v>
+        <v>101513</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 13230-2023 artfynd.xlsx
+++ b/artfynd/A 13230-2023 artfynd.xlsx
@@ -1327,7 +1327,7 @@
         <v>136298255</v>
       </c>
       <c r="B8" t="n">
-        <v>101513</v>
+        <v>101524</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 13230-2023 artfynd.xlsx
+++ b/artfynd/A 13230-2023 artfynd.xlsx
@@ -1327,7 +1327,7 @@
         <v>136298255</v>
       </c>
       <c r="B8" t="n">
-        <v>101524</v>
+        <v>101537</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 13230-2023 artfynd.xlsx
+++ b/artfynd/A 13230-2023 artfynd.xlsx
@@ -1327,7 +1327,7 @@
         <v>136298255</v>
       </c>
       <c r="B8" t="n">
-        <v>101537</v>
+        <v>101538</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 13230-2023 artfynd.xlsx
+++ b/artfynd/A 13230-2023 artfynd.xlsx
@@ -1327,7 +1327,7 @@
         <v>136298255</v>
       </c>
       <c r="B8" t="n">
-        <v>101538</v>
+        <v>101551</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 13230-2023 artfynd.xlsx
+++ b/artfynd/A 13230-2023 artfynd.xlsx
@@ -1327,7 +1327,7 @@
         <v>136298255</v>
       </c>
       <c r="B8" t="n">
-        <v>101551</v>
+        <v>101552</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
